--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486461_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486461_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1878</v>
+        <v>1.8911</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2174</v>
+        <v>4.1056</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0295</v>
+        <v>-2.2145</v>
       </c>
       <c r="G2" t="n">
         <v>1.6347</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8152</v>
+        <v>0.5185</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0601</v>
+        <v>-0.0517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7551</v>
+        <v>0.5702</v>
       </c>
       <c r="V2" t="n">
         <v>0.3904</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7048</v>
+        <v>1.2761</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6743</v>
+        <v>1.184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0304</v>
+        <v>0.0921</v>
       </c>
       <c r="G3" t="n">
         <v>1.3536</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3511</v>
+        <v>-0.0775</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3257</v>
+        <v>-0.1646</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0255</v>
+        <v>0.0871</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2684</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8697</v>
+        <v>1.1559</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.6321</v>
       </c>
       <c r="G4" t="n">
         <v>1.0833</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.793</v>
+        <v>0.0484</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8736</v>
+        <v>0.1598</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0806</v>
+        <v>-0.1115</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3904</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5824</v>
+        <v>-0.5113</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4612</v>
+        <v>-0.2741</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1212</v>
+        <v>-0.2373</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3473</v>
+        <v>0.9556</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2828</v>
+        <v>0.593</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0645</v>
+        <v>0.3626</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0182</v>
+        <v>0.876</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0182</v>
+        <v>0.876</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3291</v>
+        <v>0.0796</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2645</v>
+        <v>-0.2829</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0645</v>
+        <v>0.3626</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S5" t="n">
-        <v>0.483</v>
+        <v>-0.1842</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6081</v>
+        <v>0.155</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1251</v>
+        <v>-0.3392</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7705</v>
+        <v>-0.6942</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3177</v>
+        <v>-1.0257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5472</v>
+        <v>0.3315</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4656</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4795</v>
+        <v>-0.1875</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3921</v>
+        <v>0.1763</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9575</v>
+        <v>-0.88</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5661</v>
+        <v>-0.728</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3914</v>
+        <v>-0.152</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9556</v>
+        <v>0.3473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.593</v>
+        <v>0.2828</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3626</v>
+        <v>0.0645</v>
       </c>
       <c r="J7" t="n">
-        <v>0.876</v>
+        <v>0.0182</v>
       </c>
       <c r="K7" t="n">
-        <v>0.876</v>
+        <v>0.0182</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0796</v>
+        <v>0.3291</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2829</v>
+        <v>0.2645</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3626</v>
+        <v>0.0645</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.6525</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6303</v>
+        <v>0.1854</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.137</v>
+        <v>0.3413</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4933</v>
+        <v>-0.1559</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0337</v>
+        <v>-2.6801</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6461</v>
+        <v>-2.3541</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3876</v>
+        <v>-0.326</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5746</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1764</v>
+        <v>0.1772</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2235</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1952</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2097</v>
+        <v>-2.7319</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2563</v>
+        <v>0.1907</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9534</v>
+        <v>-2.9226</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1714</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8855</v>
+        <v>-0.4077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8904</v>
+        <v>-0.4434</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0049</v>
+        <v>0.0357</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1952</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.274</v>
+        <v>-3.59</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2704</v>
+        <v>-1.4939</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0036</v>
+        <v>-2.0961</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5935</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0052</v>
+        <v>-0.3212</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0769</v>
+        <v>-0.3004</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0717</v>
+        <v>-0.0207</v>
       </c>
       <c r="V10" t="n">
         <v>2.0647</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2382</v>
+        <v>-5.1891</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8425</v>
+        <v>-1.1014</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3957</v>
+        <v>-4.0877</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1026</v>
+        <v>-3.9417</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2069</v>
+        <v>-0.9734</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-2.9683</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1375</v>
+        <v>-1.0711</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0793</v>
+        <v>-0.1397</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0582</v>
+        <v>-0.9315</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2401</v>
+        <v>-2.8705</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2863</v>
+        <v>-0.8337</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9539</v>
+        <v>-2.0368</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6976</v>
+        <v>-2.6101</v>
       </c>
       <c r="R11" t="n">
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5053</v>
+        <v>-0.7249</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2824</v>
+        <v>-0.2451</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2229</v>
+        <v>-0.4798</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4552</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4552</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5091</v>
+        <v>-6.1435</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0207</v>
+        <v>-3.5937</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4884</v>
+        <v>-2.5498</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9417</v>
+        <v>-1.1026</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9734</v>
+        <v>-0.2069</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9683</v>
+        <v>-0.8957000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0711</v>
+        <v>0.1375</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1397</v>
+        <v>0.0793</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9315</v>
+        <v>0.0582</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8705</v>
+        <v>-1.2401</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8337</v>
+        <v>-0.2863</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0368</v>
+        <v>-0.9539</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.6101</v>
+        <v>-3.6976</v>
       </c>
       <c r="R12" t="n">
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0449</v>
+        <v>-0.4107</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1644</v>
+        <v>-0.0336</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.377</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5649999999999999</v>
+        <v>-2.4552</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2599</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.4141</v>
+        <v>-18.7292</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6196</v>
+        <v>-3.934699999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-14.7945</v>
@@ -1438,13 +1438,13 @@
         <v>-1.0044</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.4704</v>
+        <v>-4.470399999999999</v>
       </c>
       <c r="J13" t="n">
         <v>10.6273</v>
       </c>
       <c r="K13" t="n">
-        <v>5.658700000000001</v>
+        <v>5.6587</v>
       </c>
       <c r="L13" t="n">
         <v>4.9685</v>
@@ -1468,13 +1468,13 @@
         <v>10.8751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8927</v>
+        <v>-1.2078</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2316</v>
+        <v>-0.5467</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.661</v>
+        <v>-0.6611</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1713</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1052</v>
+        <v>5.0744</v>
       </c>
       <c r="E14" t="n">
         <v>5.8006</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6953</v>
+        <v>-0.7262</v>
       </c>
       <c r="G14" t="n">
         <v>2.3884</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.632</v>
+        <v>0.6011</v>
       </c>
       <c r="T14" t="n">
         <v>0.5636</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V14" t="n">
         <v>3.3899</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6639</v>
+        <v>3.9124</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6626</v>
+        <v>0.8803</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0013</v>
+        <v>3.0322</v>
       </c>
       <c r="G15" t="n">
         <v>1.9695</v>
@@ -1624,13 +1624,13 @@
         <v>3.2626</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0636</v>
+        <v>0.3121</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8172</v>
+        <v>0.0349</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2465</v>
+        <v>0.2773</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5443</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5183</v>
+        <v>3.6186</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9001</v>
+        <v>2.1236</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6183</v>
+        <v>1.495</v>
       </c>
       <c r="G16" t="n">
         <v>2.3494</v>
@@ -1702,13 +1702,13 @@
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1918</v>
+        <v>0.292</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2499</v>
+        <v>-0.0264</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4417</v>
+        <v>0.3184</v>
       </c>
       <c r="V16" t="n">
         <v>2.0647</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1027</v>
+        <v>3.0949</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5609</v>
+        <v>2.3373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.2512</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1061</v>
+        <v>-0.1139</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1286</v>
+        <v>-0.0949</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2347</v>
+        <v>-0.0189</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.099</v>
+        <v>2.7406</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0922</v>
+        <v>2.9804</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0068</v>
+        <v>-0.2398</v>
       </c>
       <c r="G18" t="n">
         <v>0.8981</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2656</v>
+        <v>0.9073</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6321</v>
+        <v>0.5203</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6335</v>
+        <v>0.3869</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3698</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.125</v>
+        <v>2.5913</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8618</v>
+        <v>4.4206</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7368</v>
+        <v>-1.8293</v>
       </c>
       <c r="G19" t="n">
         <v>3.1656</v>
@@ -1936,13 +1936,13 @@
         <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3032</v>
+        <v>0.1631</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5239</v>
+        <v>0.0349</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2207</v>
+        <v>0.1283</v>
       </c>
       <c r="V19" t="n">
         <v>-2.2599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.346</v>
+        <v>1.7686</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1081</v>
+        <v>1.7801</v>
       </c>
       <c r="F20" t="n">
-        <v>3.454</v>
+        <v>-0.0114</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6394</v>
+        <v>1.1313</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7461</v>
+        <v>1.2318</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1068</v>
+        <v>-0.1004</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3651</v>
+        <v>2.2375</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.2137</v>
+        <v>1.6821</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1514</v>
+        <v>0.5554</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2742</v>
+        <v>-1.1062</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5324</v>
+        <v>-0.4504</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2582</v>
+        <v>-0.6558</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2626</v>
+        <v>1.7401</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>3.2626</v>
+        <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3323</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1334</v>
+        <v>-0.4999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4656</v>
+        <v>-0.0379</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.26</v>
+        <v>0.9683</v>
       </c>
       <c r="E21" t="n">
-        <v>1.333</v>
+        <v>-2.3316</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0731</v>
+        <v>3.2999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1313</v>
+        <v>-2.6394</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2318</v>
+        <v>-2.7461</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1004</v>
+        <v>0.1068</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2375</v>
+        <v>-2.3651</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6821</v>
+        <v>-2.2137</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5554</v>
+        <v>-0.1514</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1062</v>
+        <v>-0.2742</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4504</v>
+        <v>-0.5324</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6558</v>
+        <v>0.2582</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7401</v>
+        <v>3.2626</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.8276</v>
+        <v>3.2626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0464</v>
+        <v>-0.0454</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9469</v>
+        <v>-0.3569</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.3115</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5232</v>
+        <v>-1.3383</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3389</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1843</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8576</v>
@@ -2170,13 +2170,13 @@
         <v>2.8276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0582</v>
+        <v>0.1268</v>
       </c>
       <c r="T22" t="n">
         <v>0.1526</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2108</v>
+        <v>-0.0258</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5438</v>
+        <v>-1.4514</v>
       </c>
       <c r="E23" t="n">
         <v>0.3083</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8521</v>
+        <v>-1.7596</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7753</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1662</v>
+        <v>0.2587</v>
       </c>
       <c r="T23" t="n">
         <v>0.3581</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1919</v>
+        <v>-0.0994</v>
       </c>
       <c r="V23" t="n">
         <v>0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7389</v>
+        <v>-1.5655</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.148</v>
+        <v>-1.0363</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5909</v>
+        <v>-0.5292</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4064</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2449</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1079</v>
+        <v>-0.0463</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>19.4142</v>
+        <v>19.4139</v>
       </c>
       <c r="E25" t="n">
-        <v>15.9245</v>
+        <v>15.9244</v>
       </c>
       <c r="F25" t="n">
-        <v>3.4897</v>
+        <v>3.489800000000001</v>
       </c>
       <c r="G25" t="n">
         <v>5.4748</v>
@@ -2404,10 +2404,10 @@
         <v>21.7507</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8927</v>
+        <v>1.8925</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6611</v>
+        <v>0.6611000000000001</v>
       </c>
       <c r="U25" t="n">
         <v>1.2316</v>
